--- a/OneDrive - GOUVCI/DCSARD/Action_Regionale/App/dashbord-Anstat-version_V2_atelier/dashbord-Anstat-version_V2_atelier/search_indicateur.xlsx
+++ b/OneDrive - GOUVCI/DCSARD/Action_Regionale/App/dashbord-Anstat-version_V2_atelier/dashbord-Anstat-version_V2_atelier/search_indicateur.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gouvci-my.sharepoint.com/personal/b_toh_stat_plan_gouv_ci/Documents/DCSARD/Action_Regionale/App/dashbord-Anstat-version_V2_atelier/dashbord-Anstat-version_V2_atelier/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive - GOUVCI\DCSARD\Action_Regionale\App\dashbord-Anstat-version_V2_atelier\dashbord-Anstat-version_V2_atelier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_10E34AD51E2A7B0DD8EDC9E747B982FFA04E4088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F72A8C09-6378-47EE-BDA2-9EF688312B06}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8473EC86-C110-4724-AB17-B36B2B5FFBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,21 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$523</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$599</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -28,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="704">
   <si>
     <t>Indicateurs</t>
   </si>
@@ -1687,6 +1698,459 @@
   </si>
   <si>
     <t>Rapport de masculinité (RM) en %</t>
+  </si>
+  <si>
+    <t>Couverture vaccinale contre la Polio</t>
+  </si>
+  <si>
+    <t>Dépenses publiques consacrées à la santé en pourcentage du budget</t>
+  </si>
+  <si>
+    <t>Incidence des maladies (Paludisme)</t>
+  </si>
+  <si>
+    <t>Nombre d’Officines de Pharmacies Privées</t>
+  </si>
+  <si>
+    <t>Nombre de Centres Hospitaliers Régionaux (CHR)</t>
+  </si>
+  <si>
+    <t>Nombre de Centres Hospitaliers Universitaires (CHU)</t>
+  </si>
+  <si>
+    <t>Nombre de lits d'hôpitaux</t>
+  </si>
+  <si>
+    <t>Nombre de lits d'hôpitaux pour 10 000 habitants</t>
+  </si>
+  <si>
+    <t>Nombre de médecins</t>
+  </si>
+  <si>
+    <t>Nombre de médecins  pour 10 000 habitants</t>
+  </si>
+  <si>
+    <t>Nombre de pharmaciens</t>
+  </si>
+  <si>
+    <t>Nombre de Pharmacies Publiques</t>
+  </si>
+  <si>
+    <t>Nombre de sages femmes</t>
+  </si>
+  <si>
+    <t>Nombre de Service de Maternité</t>
+  </si>
+  <si>
+    <t>Nombre de techniciens de laboratoires</t>
+  </si>
+  <si>
+    <t>Nombre d'établissement de référence de niveau secondaire (HG et CHR)</t>
+  </si>
+  <si>
+    <t>Nombre d'établissement sanitaire de premier contact (ESPC) publics</t>
+  </si>
+  <si>
+    <t>Nombre d'Hôpitaux Généraux</t>
+  </si>
+  <si>
+    <t>Nombre d'infirmières</t>
+  </si>
+  <si>
+    <t>Nombre d'infirmières pour 10 000 habitants</t>
+  </si>
+  <si>
+    <t>Taux brut de mortalité</t>
+  </si>
+  <si>
+    <t>Taux de mortalité infantile</t>
+  </si>
+  <si>
+    <t>Taux de mortalité infanto-juvénile</t>
+  </si>
+  <si>
+    <t>Taux de mortalité maternelle</t>
+  </si>
+  <si>
+    <t>Pauvrété</t>
+  </si>
+  <si>
+    <t>Gap de pauvreté</t>
+  </si>
+  <si>
+    <t>Nombre de non pauvre</t>
+  </si>
+  <si>
+    <t>Nombre de Pauvre</t>
+  </si>
+  <si>
+    <t>Seuil de pauvreté annuel national</t>
+  </si>
+  <si>
+    <t>Seuil de pauvreté journalier national</t>
+  </si>
+  <si>
+    <t>Sévérité de pauvreté</t>
+  </si>
+  <si>
+    <t>Taux de pauvreté - National</t>
+  </si>
+  <si>
+    <t>Taux de pauvreté - Rural</t>
+  </si>
+  <si>
+    <t>Taux de pauvreté - Urbain</t>
+  </si>
+  <si>
+    <t>Taux de pauvreté des ménages dont le chef est alphabétisé</t>
+  </si>
+  <si>
+    <t>Taux de pauvreté des ménages dont le chef est non alphabétisé</t>
+  </si>
+  <si>
+    <t>Durée moyenne (min) pour atteindre un établissement sanitaire de premier contact (ESPC)</t>
+  </si>
+  <si>
+    <t>Durée moyenne (min) pour atteindre un établissement sanitaire de référence de niveau secondaire</t>
+  </si>
+  <si>
+    <t>Durée moyenne (min) pour atteindre une infrastructure sanitaire (CHU, Institut spécialisé)</t>
+  </si>
+  <si>
+    <t>Proportion de la population résidant à moins de 5km d’un centre de santé</t>
+  </si>
+  <si>
+    <t>Proportion de la population résidant à plus de 15km d’un centre de santé</t>
+  </si>
+  <si>
+    <t>Proportion de la population résidant entre de 5km et 15km d’un centre de santé</t>
+  </si>
+  <si>
+    <t>Proportion de ménage ayant accès à l'eau de robinet</t>
+  </si>
+  <si>
+    <t>Proportion de ménages ayant accès à une source d'eau améliorée</t>
+  </si>
+  <si>
+    <t>Proportion de ménages résidant à moins de 5km d’un centre de santé</t>
+  </si>
+  <si>
+    <t>Proportion de ménages résidant à moins de 5km d’une école</t>
+  </si>
+  <si>
+    <t>Proportion des élèves du primaire selon la distance parcourue de la maison à l’école (De 3 à 5 km)</t>
+  </si>
+  <si>
+    <t>Proportion des élèves du primaire selon la distance parcourue de la maison à l’école (Moins de 3Km)</t>
+  </si>
+  <si>
+    <t>Proportion des élèves du primaire selon la distance parcourue de la maison à l’école (Plus de 5km)</t>
+  </si>
+  <si>
+    <t>Taux d’accès à l'électricité</t>
+  </si>
+  <si>
+    <t>Taux de couverture (en termes de localité) en électrification</t>
+  </si>
+  <si>
+    <t>Taux de desserte</t>
+  </si>
+  <si>
+    <t>Accès à l'éducation (Effectifs inscrits au primaire)</t>
+  </si>
+  <si>
+    <t>Indice de parité hommes-femmes primaire (ratio fille/garçon)</t>
+  </si>
+  <si>
+    <t>Indice de parité hommes-femmes secondaire (Ratio fille/garçon)</t>
+  </si>
+  <si>
+    <t>Nombre d’élèves féminins au primaire</t>
+  </si>
+  <si>
+    <t>Nombre d’élèves masculins au primaire</t>
+  </si>
+  <si>
+    <t>Nombre d’enseignantes femmes au primaire</t>
+  </si>
+  <si>
+    <t>Nombre d’enseignants hommes au primaire</t>
+  </si>
+  <si>
+    <t>Nombre d'écoles primaires</t>
+  </si>
+  <si>
+    <t>Nombre d'écoles secondaires</t>
+  </si>
+  <si>
+    <t>Nombre d'élève du secondaire de sexe féminin</t>
+  </si>
+  <si>
+    <t>Nombre d'élève du secondaire de sexe masculin</t>
+  </si>
+  <si>
+    <t>Nombre d'enseignants Femmes du niveau secondaire</t>
+  </si>
+  <si>
+    <t>Nombre d'enseignants Hommes du niveau secondaire</t>
+  </si>
+  <si>
+    <t>Ratio élèves par maître - Préscolaire</t>
+  </si>
+  <si>
+    <t>Ratio élèves par maître - Primaire</t>
+  </si>
+  <si>
+    <t>Ratio élèves par salle de classe - Préscolaire</t>
+  </si>
+  <si>
+    <t>Ratio élèves par salle de classe - Primaire</t>
+  </si>
+  <si>
+    <t>Taux brut de scolarisation au primaire</t>
+  </si>
+  <si>
+    <t>Taux d’achèvement primaire</t>
+  </si>
+  <si>
+    <t>Taux d'achèvement ou de diplomation Secondaire</t>
+  </si>
+  <si>
+    <t>Taux de réussite au BAC</t>
+  </si>
+  <si>
+    <t>Taux de réussite au BEPC</t>
+  </si>
+  <si>
+    <t>Taux de réussite au CEPE</t>
+  </si>
+  <si>
+    <t>Taux de scolarisation au Secondaire</t>
+  </si>
+  <si>
+    <t>Taux net de scolarisation au primaire</t>
+  </si>
+  <si>
+    <t>Economie</t>
+  </si>
+  <si>
+    <t>Excédent Brut d’Exploitation (EBE)</t>
+  </si>
+  <si>
+    <t>Exportation (Mds XOF)</t>
+  </si>
+  <si>
+    <t>Indice de la Production Industrielle (IPI) – Croissance annuelle</t>
+  </si>
+  <si>
+    <t>Indice des Prix à la Production de l'Industrie (IPPI) – Croissance annuelle</t>
+  </si>
+  <si>
+    <t>Indice du Chiffre d'Affaires (ICA) commerce (glissement annuel )</t>
+  </si>
+  <si>
+    <t>Indice du Chiffre d'Affaires (ICA) industrie (glissement annuel )</t>
+  </si>
+  <si>
+    <t>Inflation annuelle moyenne (IHPC – ANStat)</t>
+  </si>
+  <si>
+    <t>Investissements Directs Étrangers(IDE) – CREDIT</t>
+  </si>
+  <si>
+    <t>Investissements Directs Étrangers(IDE) – DEBIT</t>
+  </si>
+  <si>
+    <t>Nombre d’entreprises formelles</t>
+  </si>
+  <si>
+    <t>Part d’emplois nationaux</t>
+  </si>
+  <si>
+    <t>Part d’emplois permanents</t>
+  </si>
+  <si>
+    <t>Part de femmes dans l’emploi</t>
+  </si>
+  <si>
+    <t>Part des exportations dans le PIB</t>
+  </si>
+  <si>
+    <t>PIB/habitants</t>
+  </si>
+  <si>
+    <t>Produit Intérieur Brut (PIB)</t>
+  </si>
+  <si>
+    <t>Proportion de PME</t>
+  </si>
+  <si>
+    <t>Revenu National Brut (RNB)</t>
+  </si>
+  <si>
+    <t>Revenu National Disponible Brut (RNDB)</t>
+  </si>
+  <si>
+    <t>RNB/Habitant</t>
+  </si>
+  <si>
+    <t>RNDB/Habitant</t>
+  </si>
+  <si>
+    <t>Taux de croissance du PIB</t>
+  </si>
+  <si>
+    <t>Taux de croissance réelle (Industries (Agro alimentaire,petrolière,etc…))</t>
+  </si>
+  <si>
+    <t>Taux de croissance réelle (Industries extractives)</t>
+  </si>
+  <si>
+    <t>Taux de croissance réelle (Secteur primaire)</t>
+  </si>
+  <si>
+    <t>Taux de croissance réelle (Secteur Secondaire)</t>
+  </si>
+  <si>
+    <t>Taux de croissance réelle (Secteur tertiaire)</t>
+  </si>
+  <si>
+    <t>Taux de rentabilité économique</t>
+  </si>
+  <si>
+    <t>Densité de la population</t>
+  </si>
+  <si>
+    <t>Espérance de vie à la naissance</t>
+  </si>
+  <si>
+    <t>Fécondité - Taux brut de natalité</t>
+  </si>
+  <si>
+    <t>Indice synthétique de fécondité (ISF)</t>
+  </si>
+  <si>
+    <t>Nombre de ménages en Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>Population de  0-14 ans</t>
+  </si>
+  <si>
+    <t>Population de  15-59 ans</t>
+  </si>
+  <si>
+    <t>Population de 60 ans et plus</t>
+  </si>
+  <si>
+    <t>Population de la Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>Population femme</t>
+  </si>
+  <si>
+    <t>Population homme</t>
+  </si>
+  <si>
+    <t>Proportion de la population rurale</t>
+  </si>
+  <si>
+    <t>Proportion de la population urbaine</t>
+  </si>
+  <si>
+    <t>Proportion de ménages dont le chef de ménage est un femme</t>
+  </si>
+  <si>
+    <t>Proportion de ménages dont le chef de ménage est un homme</t>
+  </si>
+  <si>
+    <t>Rapport de masculinité</t>
+  </si>
+  <si>
+    <t>Taille moyenne des ménages</t>
+  </si>
+  <si>
+    <t>Taux d’urbanisation</t>
+  </si>
+  <si>
+    <t>Taux d'analphabétisme de la population de 15 ans et plus</t>
+  </si>
+  <si>
+    <t>Taux de croissance démographique</t>
+  </si>
+  <si>
+    <t>Indice de Perception de la Corruption (IPC)</t>
+  </si>
+  <si>
+    <t>Proportion de la population satisfaite du fonctionnement de la démocratie</t>
+  </si>
+  <si>
+    <t>Justice</t>
+  </si>
+  <si>
+    <t>Indice de Gini - National</t>
+  </si>
+  <si>
+    <t>Indice de Gini - rural</t>
+  </si>
+  <si>
+    <t>Indice de Gini - Urbain</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 1 (10% des plus pauvre)</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 10 (10% des plus riches)</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 2</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 3</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 4</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 5</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 6</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 7</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 8</t>
+  </si>
+  <si>
+    <t>Part de la consommation annuelle - Décile 9</t>
+  </si>
+  <si>
+    <t>Inégalité</t>
+  </si>
+  <si>
+    <t>Emploi</t>
+  </si>
+  <si>
+    <t>Durée moyenne du chômage</t>
+  </si>
+  <si>
+    <t>Taux de chômage Abidjan</t>
+  </si>
+  <si>
+    <t>Taux de chômage autres villes</t>
+  </si>
+  <si>
+    <t>Taux de chômage femme</t>
+  </si>
+  <si>
+    <t>Taux de chômage global</t>
+  </si>
+  <si>
+    <t>Taux de chômage homme</t>
+  </si>
+  <si>
+    <t>Taux de chômage rural</t>
   </si>
 </sst>
 </file>
@@ -1705,18 +2169,24 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1739,21 +2209,124 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1945,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C523"/>
+  <dimension ref="A1:C669"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.7265625" customWidth="1"/>
@@ -7707,8 +8280,1746 @@
         <v>535</v>
       </c>
     </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A524" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C524" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A525" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C525" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A526" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C526" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A527" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C527" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A528" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C528" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A529" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C529" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A530" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C530" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A531" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C531" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A532" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C532" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A533" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C533" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A534" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C534" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A535" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C535" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A536" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C536" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A537" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C537" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A538" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C538" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A539" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C539" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A540" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C540" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A541" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C541" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A542" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C542" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A543" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C543" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A544" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C544" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A545" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C545" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A546" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C546" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A547" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C547" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A548" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C548" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A549" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C549" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A550" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C550" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A551" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C551" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A552" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C552" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A553" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C553" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A554" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C554" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A555" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C555" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A556" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C556" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A557" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C557" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A558" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C558" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A559" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C559" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A560" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C560" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A561" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C561" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A562" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C562" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A563" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C563" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A564" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C564" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A565" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C565" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A566" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="B566" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C566" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A567" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C567" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A568" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C568" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A569" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C569" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A570" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C570" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A571" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C571" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A572" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C572" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A573" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C573" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A574" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B574" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C574" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A575" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B575" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C575" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A576" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C576" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A577" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="B577" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A578" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="B578" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C578" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A579" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B579" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A580" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C580" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A581" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A582" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C582" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A583" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C583" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A584" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C584" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A585" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C585" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A586" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C586" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A587" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C587" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A588" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C588" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A589" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C589" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A590" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C590" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A591" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C591" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A592" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C592" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A593" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C593" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A594" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C594" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A595" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C595" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A596" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C596" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A597" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="B597" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C597" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A598" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="B598" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C598" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A599" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C599" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A600" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C600" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A601" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C601" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A602" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C602" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A603" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C603" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A604" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C604" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A605" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C605" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A606" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C606" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A607" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C607" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A608" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C608" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A609" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C609" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A610" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C610" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A611" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C611" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A612" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C612" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A613" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C613" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A614" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C614" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A615" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C615" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A616" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C616" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A617" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C617" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A618" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C618" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A619" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C619" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A620" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C620" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A621" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C621" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A622" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C622" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A623" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C623" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A624" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C624" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A625" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C625" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A626" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C626" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A627" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C627" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A628" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B628" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C628" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A629" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="B629" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C629" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A630" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="B630" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C630" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A631" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="B631" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C631" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A632" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B632" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C632" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A633" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B633" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C633" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A634" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="B634" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C634" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A635" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B635" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C635" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A636" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="B636" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C636" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A637" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="B637" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C637" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A638" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="B638" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C638" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A639" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B639" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C639" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A640" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="B640" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C640" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A641" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="B641" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C641" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A642" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="B642" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C642" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A643" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B643" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C643" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A644" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="B644" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C644" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A645" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="B645" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C645" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A646" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="B646" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C646" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A647" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="B647" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C647" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A648" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B648" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C648" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A649" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="B649" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C649" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A650" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C650" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A651" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="B651" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C651" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A652" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C652" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A653" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="B653" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C653" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A654" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C654" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A655" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C655" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A656" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C656" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A657" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C657" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A658" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C658" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A659" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C659" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A660" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C660" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A661" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C661" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A662" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C662" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A663" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="B663" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C663" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A664" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="B664" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C664" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A665" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="B665" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C665" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A666" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="B666" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C666" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A667" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="B667" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C667" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A668" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B668" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C668" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A669" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="B669" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C669" t="s">
+        <v>696</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C523" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C599" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="A524:A547">
+    <cfRule type="duplicateValues" dxfId="11" priority="31"/>
+    <cfRule type="duplicateValues" priority="32"/>
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A548:A558">
+    <cfRule type="duplicateValues" dxfId="9" priority="28"/>
+    <cfRule type="duplicateValues" priority="29"/>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A559:A567">
+    <cfRule type="duplicateValues" dxfId="8" priority="25"/>
+    <cfRule type="duplicateValues" priority="26"/>
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A568:A571">
+    <cfRule type="duplicateValues" dxfId="7" priority="22"/>
+    <cfRule type="duplicateValues" priority="23"/>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A572:A574">
+    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
+    <cfRule type="duplicateValues" priority="20"/>
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A575:A599">
+    <cfRule type="duplicateValues" dxfId="5" priority="16"/>
+    <cfRule type="duplicateValues" priority="17"/>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A600:A627">
+    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
+    <cfRule type="duplicateValues" priority="14"/>
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A628:A647">
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+    <cfRule type="duplicateValues" priority="11"/>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A648:A649">
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" priority="8"/>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A650:A662">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" priority="5"/>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A663:A669">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" priority="2"/>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
